--- a/YouTube이슈분석_개인채널_2026-07-25.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-25.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
   <si>
     <t>날짜</t>
   </si>
@@ -77,60 +77,90 @@
     <t>한국</t>
   </si>
   <si>
+    <t>사건사고</t>
+  </si>
+  <si>
+    <t>608일.. 동굴에 갇힌 남자가 발견됐을 때</t>
+  </si>
+  <si>
+    <t>다큐스토리 844</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>8:37</t>
+  </si>
+  <si>
+    <t>본 영상은 608일이라는 긴 시간 동안 동굴에 갇혔던 남자의 실화를 다룬 다큐멘터리입니다. 성냥갑, 전기 램프, 옷 조각과 신발 등 현장에서 발견된 유품들을 통해 고립 당시의 상황을 재구성하며, 사고의 전말과 생존 과정에서의 비극적인 흔적들을 되짚어보는 내용을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용한 콘텐츠이므로 실제 역사적 사건의 구체적인 사실관계는 제공된 링크의 공식 자료를 교차 검증하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>▶</t>
+  </si>
+  <si>
+    <t>메타데이터+자막(Gemini)</t>
+  </si>
+  <si>
+    <t>【일사사】  생방송 중 55차례 공격한 살인범이 일본에서 동정받는 이유</t>
+  </si>
+  <si>
+    <t>테가미 | 일본 사건사고</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2025년 3월 도쿄에서 발생한 스트리머 살인 사건을 다룹니다. 가해자가 방송 중 피해자를 55회 공격해 살해했으나, 재판 과정에서 거액의 대여금 문제와 압류 등 경제적 갈등이 드러나며 일본 여론이 요동쳤습니다. 법원은 범행의 잔혹함과 피해 유발 요인을 동시에 고려해 징역 16년을 선고했습니다. 본 영상은 사건의 전말과 배경, 사회적 반응을 객관적으로 분석하며 스트리머와 시청자 간의 위험한 관계성을 조명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 스트리머와 팬 사이의 과도한 사적 교류와 금전 거래가 치명적인 범죄로 이어질 수 있다는 사회적 경각심을 강조합니다.</t>
+  </si>
+  <si>
+    <t>[중국실화] 존경받던 군인에서 연쇄 살인마로.. 그가 변한 이유는?</t>
+  </si>
+  <si>
+    <t>유팬더 - 사건실화</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>본 영상은 중국에서 존경받던 군인 출신 인물이 연쇄 살인마로 돌변하게 된 충격적인 사건인 '항저우 여회계사 토막 살인 사건'을 다룹니다. 한때 명예로운 군인이었던 그가 왜 극악무도한 범죄를 저지르게 되었는지 사건의 배경과 경과, 그리고 범인의 심리 상태를 면밀히 분석하며 사건의 전말을 상세히 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 사건을 바탕으로 한 범죄 추리 콘텐츠로, 자극적인 내용을 포함하고 있으므로 시청 시 유의하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>大阪バイク窃盗未遂　犯人の親が逆ギレ・脅迫するも垢消して逃亡 【ゆっくり解説】</t>
+  </si>
+  <si>
+    <t>ゆっくり事件アーカイブ</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>오사카에서 발생한 오토바이 절도 미수 사건을 다룹니다. 범인의 부모가 잘못을 반성하기는커녕 도리어 적반하장격으로 피해자를 협박하며 논란이 되었습니다. 이후 여론의 비판을 견디지 못한 부모가 SNS 계정을 삭제하고 잠적한 사건의 전말과 그 파장을 짚어봅니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 조회수를 유도하는 사건사고 요약 채널의 전형적인 클릭베이트 형식을 띠고 있습니다.</t>
+  </si>
+  <si>
+    <t>미국</t>
+  </si>
+  <si>
     <t>핫이슈</t>
   </si>
   <si>
-    <t>이수지 SNS 근황 난리났다ㄷㄷ "재선거? 싸움에 술판.. 제헌절 올공 집회 논란" ('핫이슈지' 공무원 패러디에 윤 어게인 억까)</t>
-  </si>
-  <si>
-    <t>알리미 황희두</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>해당 영상은 개그우먼 이수지가 공무원 패러디 및 윤석열 대통령 성대모사 등으로 주목받는 가운데, 제헌절 올림픽공원 집회 참여 논란 등 SNS상의 뜨거운 반응과 이에 얽힌 정치적 견해를 다룹니다. 황희두는 이러한 이슈를 통해 대중문화 내 정치 풍자와 이를 둘러싼 비판 및 옹호 여론을 심층 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 시청자의 호기심을 유발하는 정치적 견해 중심의 콘텐츠이므로 객관적 사실관계를 추가로 확인하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>▶</t>
-  </si>
-  <si>
-    <t>메타데이터+자막(Gemini)</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>사건사고</t>
-  </si>
-  <si>
-    <t>【千葉点滴殺人事件】患者の点滴に排泄物混入か…元看護師の不可解な行動【かなえ先生の切り抜き】元配信2026/07/16</t>
-  </si>
-  <si>
-    <t>【公認】かなえ先生への共感【Vtuber】</t>
-  </si>
-  <si>
-    <t>15:47</t>
-  </si>
-  <si>
-    <t>본 영상은 지바현에서 발생한 전직 간호사의 점적 정맥주사 배설물 혼입 살인 사건을 다룹니다. 가해자의 비상식적인 범행 동기와 스마트폰 검색 기록 등 결정적 증거, 유사한 과거 의료 범죄 사례를 분석하며, 카나에 선생이 의료인으로서의 윤리적 문제와 사건의 충격적인 이면을 비판적으로 고찰하는 내용입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 실제 의료 현장에서 발생하는 강력 범죄의 기괴한 특성과 수사 과정을 다루므로 시청 시 심리적 주의가 필요합니다.</t>
-  </si>
-  <si>
-    <t>미국</t>
-  </si>
-  <si>
     <t>She Definitely Didn't Think This Through...</t>
   </si>
   <si>
@@ -143,10 +173,25 @@
     <t>15:39</t>
   </si>
   <si>
-    <t>이 영상은 현대 데이트 문화와 관계에서 발생하는 복잡한 역학 관계를 다룹니다. 특히 첫 데이트에서의 지나친 기대치, 재정적 부담, 그리고 연애 과정에서 나타나는 다양한 경고 신호(레드 플래그)에 대한 솔직한 의견을 공유하며, 미성숙한 데이트 태도가 관계에 미치는 부정적인 영향을 비판적으로 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️자극적인 제목의 클립을 소비할 때는 특정 개인의 사례를 일반화하지 말고 보편적인 인간관계의 예절과 상호 존중의 관점에서 해석하는 것이 중요합니다.</t>
+    <t>이 영상은 현대 데이트 문화와 관계의 복잡한 역학을 다룹니다. 특히 첫 데이트에서의 지나친 기대치와 경제적 부담, 데이트 중 나타나는 위험 신호(Red Flags)에 대해 가감 없는 비판적 시각을 제시합니다. 무리한 소비를 조장하는 현대 데이트 기준의 문제점을 지적하며, 건강한 관계를 위한 현실적인 조언과 분석을 제공하는 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 클릭베이트 형식을 띠고 있으므로, 영상 속 주장을 있는 그대로 받아들이기보다 본인의 가치관에 비추어 비판적으로 수용하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Viral TikTok Funny Videos Reaction 😂 | Pashto Comedy Compilation</t>
+  </si>
+  <si>
+    <t>Metal</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>이 영상은 파슈토어권 틱톡의 인기 코미디 영상들을 모아 제작자의 리액션을 곁들인 편집본입니다. 게임, 드라마 리뷰 등 다양한 엔터테인먼트 콘텐츠를 다루는 Metal 채널에서 제작했으며, 타인의 콘텐츠를 재구성한 리액션 비디오 형식을 취하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트 성격이 강한 리액션 영상이므로 유머 위주의 가벼운 감상용으로 시청하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>Racist Hispanic Man Walked Into a Black Community... He Immediately Regretted It</t>
@@ -155,16 +200,13 @@
     <t>VoxGlobe</t>
   </si>
   <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
     <t>19:17</t>
   </si>
   <si>
-    <t>본 영상은 흑인 거주 지역에서 인종차별적 발언을 한 히스패닉 남성과 지역 주민들 간의 충돌 사건을 다룹니다. 이 영상은 사건의 전말과 그에 따른 대중의 반응을 분석하며, 현대 사회의 인종 문제, 상호 존중, 그리고 책임에 관한 폭넓은 사회적 논의를 이끌어내는 데 초점을 맞추고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 썸네일로 조회수를 유도하는 클릭베이트 성격의 영상일 수 있으니 사실관계 확인에 유의하세요.</t>
+    <t>이 영상은 히스패닉 남성이 흑인 거주 지역에서 인종차별적 발언을 해 현지 주민들과 충돌을 빚은 바이럴 사건을 다룹니다. 영상은 사건의 전말과 그에 따른 대중의 반응을 분석하며, 인종 간의 존중과 사회적 책임에 대한 논의를 촉구하고 다양한 관점을 조명하는 사회적 논평 형식의 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일로 시청을 유도하는 클릭베이트 성향이 강하므로, 정보의 사실관계보다는 사건에 대한 대중의 반응과 사회적 맥락을 위주로 비판적 시각을 갖고 시청하십시오.</t>
   </si>
   <si>
     <t>Advocate Rajini Comments on Home Minister Anitha about Guntur Incident | YT18 News</t>
@@ -176,106 +218,88 @@
     <t>8:53</t>
   </si>
   <si>
-    <t>본 영상은 안드라프라데시주 군투르(Guntur) 지역에서 발생한 사건과 관련하여, 라지니 변호사가 아니타(Anitha) 내무장관의 대응과 처신을 비판하는 내용을 다룬 YT18의 정치 뉴스입니다. 지역 내 치안 및 행정 책임 문제에 대한 법률 전문가의 시각을 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 정치적 논평을 담고 있는 뉴스이므로, 사건의 전후 맥락을 파악하기 위해 다수의 언론사 보도를 교차 검증하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>Ừ Thì Xe Phần 415 : Uống cà phê vào thì đỡ lao lên vỉa hè | @uthixe​</t>
-  </si>
-  <si>
-    <t>Ừ Thì Xe</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>이 영상은 도로 위에서 벌어지는 황당하고 위험한 교통 상황들을 모아 분석한 블랙박스 모음집입니다. 운전자들의 부주의로 발생하는 다양한 사고와 실수 장면을 통해 교통안전의 중요성을 강조하며, 유머러스한 해설을 곁들여 운전자가 지켜야 할 주의사항을 경각심 있게 전달하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 도로 위에서는 잠시의 방심이 큰 사고로 이어질 수 있으므로 항상 전방 주시와 안전거리를 유지해야 합니다.</t>
+    <t>본 영상은 유튜브 채널 YT18에서 제공하는 뉴스 콘텐츠로, 라지니 변호사가 최근 발생한 군투르 사건과 관련하여 아니타 내무부 장관의 대응 및 발언을 비판적으로 분석하는 내용을 담고 있습니다. 정치적 책임론과 공공 안전 문제를 중심으로 현지 여론과 법적 관점에서의 해석을 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 정치 뉴스 형식을 취하고 있으므로 특정 정파의 주장에 치우칠 가능성을 염두에 두고 객관적인 사실 관계를 교차 검증하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t xml:space="preserve">BTS #viral </t>
-  </si>
-  <si>
-    <t>Grace Perry Tv</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>4:36</t>
-  </si>
-  <si>
-    <t>본 영상은 방탄소년단(BTS)의 이미지를 활용한 짧은 형식의 숏폼 콘텐츠로, 구체적인 메시지나 정보 없이 단순히 멤버들의 모습을 보여주는 팬심 기반의 바이럴 영상입니다. 특정 상황이나 인터뷰 없이 음악과 함께 편집된 전형적인 조회수 유도형 짧은 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 단순 이미지 편집 위주의 클릭베이트성 영상이므로 실질적인 정보나 최신 소식을 기대하기보다는 가볍게 즐기는 용도로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>「彼らはショウヘイのような先生がいて感謝すべきだ…」試合後、大谷がフィリーズの選手たちの肩を“直接操る”姿を見てマックス・マンシーが大爆笑…その裏にある理由にMLBメディアが騒然！</t>
-  </si>
-  <si>
-    <t>FJサッカー速報</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>경기 후 대타자 오타니 쇼헤이가 필리스 선수들에게 기술을 직접 지도하는 이례적인 장면이 포착되었습니다. 철저한 정보 공유 차단이 일반적인 MLB에서 오타니가 적군에게도 노하우를 전수한 것은 그의 독보적인 인품과 야구에 대한 순수한 열정을 보여줍니다. 이를 본 맥스 먼시는 폭소를 터뜨렸고, 현지 매체와 야구계는 적까지 아우르는 오타니의 초월적인 영향력에 큰 충격을 받았습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 자극적인 제목과 과장된 묘사를 사용하는 전형적인 클릭베이트 형식이므로, 단순한 팬심이나 가벼운 에피소드를 다룬 콘텐츠로 이해하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【大炎上】日本女子バレー敗退…石川真佑の一言に賛否が真っ二つ</t>
-  </si>
-  <si>
-    <t>佐藤ニュース</t>
-  </si>
-  <si>
-    <t>23:47</t>
-  </si>
-  <si>
-    <t>일본 여자 배구 대표팀의 네이션스 리그 브라질전 패배 이후, 언론의 미화 보도와 달리 온라인상에서는 선수들의 표정과 감독의 석연치 않은 전술 운용을 두고 팀 내부 불화설 등 다양한 논란이 제기되고 있습니다. 특히 이시카와 마유의 발언을 두고 팬들 사이에서 찬반 여론이 팽팽하게 갈리며 큰 화제가 되고 있는 상황을 다루고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 커뮤니티의 반응을 편집한 오락용 콘텐츠이므로, 자극적인 제목에 현혹되지 말고 경기 내용에 대한 객관적인 정보를 교차 검증하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Khan Collage Friend Expose Family Lies| Maria Parents Did Fight In Collage </t>
-  </si>
-  <si>
-    <t>Spill Buzz Tv</t>
-  </si>
-  <si>
-    <t>7:46</t>
-  </si>
-  <si>
-    <t>본 영상은 최근 마리아 칸이 소셜 미디어와 대학을 떠나기로 결정하며 발생한 논란을 상세히 다룹니다. 영상에서는 가족들의 입장 발표와 온라인상에서 유포되는 주장들, 그리고 대중들의 반응을 분석하며 마리아 칸을 둘러싼 복잡한 사건의 경위와 그 배후에 숨겨진 이야기들을 비판적으로 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 자극적인 폭로와 루머를 다루는 클릭베이트 채널의 콘텐츠이므로 정보의 객관성에 주의하여 시청하시기 바랍니다.</t>
-  </si>
-  <si>
-    <t>Bhojpuri Nonstop Dhamaka Dj Remix  nonstopstop king || Top Viral Bhojpuri Dj Song || #bhojpuri #dj</t>
-  </si>
-  <si>
-    <t>rigan music</t>
-  </si>
-  <si>
-    <t>31:28</t>
-  </si>
-  <si>
-    <t>본 영상은 최신 유행하는 보즈푸리(Bhojpuri) 음악들을 DJ 리믹스 버전으로 엮은 논스톱 댄스 곡 모음집입니다. 고유의 경쾌한 비트와 리듬이 강조된 이 곡들은 인도 지역 파티나 축제 현장에서 인기 있는 스타일로, 끊김 없는 편집을 통해 흥겨운 분위기를 극대화한 것이 특징입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 키워드와 함께 리믹스 음원을 모아놓은 전형적인 클릭베이트형 콘텐츠이므로, 음질이 불안정할 수 있다는 점을 참고하세요.</t>
+    <t>Maria Khan’s Friend Finally REVEALS the Truth? 😳 What REALLY Happened Behind the Scenes!</t>
+  </si>
+  <si>
+    <t>Nida Shaikh</t>
+  </si>
+  <si>
+    <t>6:33</t>
+  </si>
+  <si>
+    <t>본 영상은 마리아 칸(Maria Khan)을 둘러싼 논란을 다룹니다. 그녀의 대학 동창이라 주장하는 인물의 폭로와 가족의 공식 입장 사이의 간극을 분석하며, 그녀가 소셜 미디어를 떠나게 된 진짜 이유와 파편화된 진실들을 객관적인 관점에서 파헤칩니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 폭로성 콘텐츠이므로 사실관계가 검증되지 않은 정보에 대해서는 비판적인 시각으로 접근하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>TIKTOK MASHUP VIRAL JULY 2026 PHILIPPINES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brosica mashup </t>
+  </si>
+  <si>
+    <t>4:01</t>
+  </si>
+  <si>
+    <t>이 영상은 2026년 7월 필리핀에서 유행한 틱톡의 인기 영상들을 하나로 모은 매시업 콘텐츠입니다. 바이럴 댄스부터 재미있는 상황극까지 현재 트렌드를 이끄는 핵심 영상들을 빠르게 편집하여 시청자들에게 압축된 재미를 제공하며, 최신 유행을 한눈에 파악할 수 있도록 제작되었습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 이 영상은 클릭을 유도하는 자극적인 제목과 문구를 사용하고 있으므로 실제 트렌드 반영 여부를 확인하며 시청하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>Bharat News Studio Live | Hindi Breaking News</t>
+  </si>
+  <si>
+    <t xml:space="preserve">News Fair </t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>본 영상은 'Bharat News Studio Live'라는 제목으로 송출되는 인도 기반의 실시간 뉴스 스트리밍입니다. 주로 힌디어로 진행되며, 정치, 사회, 국제 이슈 등 인도 전역의 주요 속보를 실시간으로 전달하는 것을 목적으로 합니다. 특정 주제에 대한 심층 보도보다는 뉴스 채널의 실시간 보도 형식에 집중하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트나 선정적인 제목을 사용하여 시청자를 유도하는 경우가 많으므로 실시간 정보 확인 시 공식 매체와 대조하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>Bigo HotGirl streaming 😍sexy periscope live🔥#periscope #bigolivestreaming #tango #viral #dance EP-14</t>
+  </si>
+  <si>
+    <t>American Hub</t>
+  </si>
+  <si>
+    <t>5:37</t>
+  </si>
+  <si>
+    <t>이 영상은 Bigo Live와 Periscope 등 다양한 플랫폼에서 활동하는 여성 스트리머의 영상을 편집한 14번째 에피소드입니다. 주로 스트리머의 댄스와 노출이 포함된 퍼포먼스를 강조하고 있으며, 시청자의 클릭을 유도하기 위한 자극적인 썸네일과 제목으로 구성된 바이럴 홍보성 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 썸네일과 제목을 사용하여 클릭을 유도하는 클릭베이트 콘텐츠이므로 시청 시 주의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>【海外の反応】ずっと憧れていた日本へ旅立ったフランス人女性｜少し大げさだと思っていた称賛が、現実になった瞬間…</t>
+  </si>
+  <si>
+    <t>夢だった日本へ</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>프랑스인 여성 조아나가 어머니와 함께 평소 꿈꿔왔던 일본 여행을 떠나는 영상입니다. 도쿄와 가와구치코를 방문하며 일본의 풍경, 문화, 음식, 평온한 일상을 직접 경험합니다. 여행 전에는 일본에 대한 찬사가 다소 과장되었다고 생각했던 그녀가, 실제 현지에서의 특별한 경험을 통해 일본이 왜 많은 이들에게 사랑받는 장소인지 그 진정한 매력을 깊이 이해하게 되는 과정을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 감동적인 여행기를 표방하지만, 전형적인 일본 홍보용 국뽕 콘텐츠의 특징을 띠고 있으므로 객관적인 정보보다는 주관적인 찬사 위주의 영상임을 참고하세요.</t>
   </si>
 </sst>
 </file>
@@ -362,11 +386,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -747,34 +771,34 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>21965</v>
+        <v>131394</v>
       </c>
       <c r="J2" s="3">
-        <v>3201</v>
+        <v>2253</v>
       </c>
       <c r="K2" s="3">
-        <v>122</v>
+        <v>297</v>
       </c>
       <c r="L2" s="3">
-        <v>7639</v>
+        <v>33453</v>
       </c>
       <c r="M2" s="3">
-        <v>615000</v>
-      </c>
-      <c r="N2" s="2" t="s">
+        <v>176000</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -782,55 +806,55 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="2">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="3">
+        <v>53053</v>
+      </c>
+      <c r="J3" s="3">
+        <v>524</v>
+      </c>
+      <c r="K3" s="3">
+        <v>287</v>
+      </c>
+      <c r="L3" s="3">
+        <v>25598</v>
+      </c>
+      <c r="M3" s="3">
+        <v>9780</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="O3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="P3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="3">
-        <v>65418</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1015</v>
-      </c>
-      <c r="K3" s="3">
-        <v>174</v>
-      </c>
-      <c r="L3" s="3">
-        <v>8240</v>
-      </c>
-      <c r="M3" s="3">
-        <v>173000</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -838,55 +862,55 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="3">
+        <v>30749</v>
+      </c>
+      <c r="J4" s="3">
+        <v>291</v>
+      </c>
+      <c r="K4" s="3">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3">
+        <v>6250</v>
+      </c>
+      <c r="M4" s="3">
+        <v>9630</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="P4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="3">
-        <v>98830</v>
-      </c>
-      <c r="J4" s="3">
-        <v>2460</v>
-      </c>
-      <c r="K4" s="3">
-        <v>226</v>
-      </c>
-      <c r="L4" s="3">
-        <v>16974</v>
-      </c>
-      <c r="M4" s="3">
-        <v>121000</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -894,55 +918,55 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3">
+        <v>28090</v>
+      </c>
+      <c r="J5" s="3">
+        <v>933</v>
+      </c>
+      <c r="K5" s="3">
+        <v>281</v>
+      </c>
+      <c r="L5" s="3">
+        <v>11161</v>
+      </c>
+      <c r="M5" s="3">
+        <v>10500</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="P5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="3">
-        <v>24798</v>
-      </c>
-      <c r="J5" s="3">
-        <v>440</v>
-      </c>
-      <c r="K5" s="3">
-        <v>58</v>
-      </c>
-      <c r="L5" s="3">
-        <v>12429</v>
-      </c>
-      <c r="M5" s="3">
-        <v>8780</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -950,55 +974,55 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="3">
+        <v>102126</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2527</v>
+      </c>
+      <c r="K6" s="3">
+        <v>233</v>
+      </c>
+      <c r="L6" s="3">
+        <v>15740</v>
+      </c>
+      <c r="M6" s="3">
+        <v>121000</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.84</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="3">
-        <v>40745</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>31</v>
-      </c>
-      <c r="L6" s="3">
-        <v>4027</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1710000</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1006,55 +1030,167 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="3">
+        <v>20473</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1967</v>
+      </c>
+      <c r="K7" s="3">
+        <v>252</v>
+      </c>
+      <c r="L7" s="3">
+        <v>22339</v>
+      </c>
+      <c r="M7" s="3">
+        <v>148000</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="3">
+        <v>29949</v>
+      </c>
+      <c r="J8" s="3">
+        <v>530</v>
+      </c>
+      <c r="K8" s="3">
+        <v>66</v>
+      </c>
+      <c r="L8" s="3">
+        <v>8089</v>
+      </c>
+      <c r="M8" s="3">
+        <v>8970</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="3">
+        <v>41321</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>31</v>
       </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="3">
-        <v>23122</v>
-      </c>
-      <c r="J7" s="3">
-        <v>627</v>
-      </c>
-      <c r="K7" s="3">
-        <v>53</v>
-      </c>
-      <c r="L7" s="3">
-        <v>3274</v>
-      </c>
-      <c r="M7" s="3">
-        <v>41900</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="L9" s="3">
+        <v>3721</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1710000</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1065,6 +1201,8 @@
     <hyperlink ref="Q5" r:id="rId4"/>
     <hyperlink ref="Q6" r:id="rId5"/>
     <hyperlink ref="Q7" r:id="rId6"/>
+    <hyperlink ref="Q8" r:id="rId7"/>
+    <hyperlink ref="Q9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1136,55 +1274,55 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I2" s="3">
-        <v>54302</v>
+        <v>51990</v>
       </c>
       <c r="J2" s="3">
-        <v>208</v>
+        <v>299</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>693</v>
-      </c>
-      <c r="N2" s="5">
-        <v>78</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>66</v>
+        <v>126</v>
+      </c>
+      <c r="N2" s="4">
+        <v>413</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1192,55 +1330,55 @@
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I3" s="3">
-        <v>101018</v>
+        <v>86544</v>
       </c>
       <c r="J3" s="3">
-        <v>482</v>
+        <v>209</v>
       </c>
       <c r="K3" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>1610</v>
-      </c>
-      <c r="N3" s="5">
-        <v>63</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>71</v>
+        <v>716</v>
+      </c>
+      <c r="N3" s="4">
+        <v>121</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1248,55 +1386,55 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I4" s="3">
-        <v>63631</v>
+        <v>144943</v>
       </c>
       <c r="J4" s="3">
-        <v>1164</v>
+        <v>770</v>
       </c>
       <c r="K4" s="3">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>1530</v>
-      </c>
-      <c r="N4" s="5">
-        <v>42</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>76</v>
+        <v>1240</v>
+      </c>
+      <c r="N4" s="4">
+        <v>117</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1304,55 +1442,55 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I5" s="3">
-        <v>99248</v>
+        <v>135521</v>
       </c>
       <c r="J5" s="3">
-        <v>1199</v>
+        <v>1421</v>
       </c>
       <c r="K5" s="3">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>4890</v>
-      </c>
-      <c r="N5" s="5">
-        <v>20</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>81</v>
+        <v>1360</v>
+      </c>
+      <c r="N5" s="4">
+        <v>100</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1360,55 +1498,55 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I6" s="3">
-        <v>69781</v>
+        <v>76689</v>
       </c>
       <c r="J6" s="3">
-        <v>414</v>
+        <v>1082</v>
       </c>
       <c r="K6" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>4580</v>
-      </c>
-      <c r="N6" s="5">
-        <v>15</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>86</v>
+        <v>1870</v>
+      </c>
+      <c r="N6" s="4">
+        <v>41</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
